--- a/real_pro_av_companies.xlsx
+++ b/real_pro_av_companies.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leahw\Cursor Workspaces\Supplier Risk Monitor\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D088BE-3E47-4291-BF1A-1EB1BC35AB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$660</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -2797,11 +2806,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2839,13 +2848,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2883,7 +2900,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2917,6 +2934,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2951,9 +2969,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3126,11 +3145,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K660"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="10" max="10" width="30.53125" customWidth="1"/>
+    <col min="11" max="11" width="20.53125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3165,7 +3188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3182,10 +3205,10 @@
         <v>793</v>
       </c>
       <c r="F2" s="1">
-        <v>46251.40149305556</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>46251.401493055557</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3202,10 +3225,10 @@
         <v>793</v>
       </c>
       <c r="F3" s="1">
-        <v>46251.40344907407</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>46251.403449074067</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -3222,7 +3245,7 @@
         <v>793</v>
       </c>
       <c r="F4" s="1">
-        <v>46251.42671296297</v>
+        <v>46251.426712962973</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -3234,10 +3257,10 @@
         <v>795</v>
       </c>
       <c r="K4" s="1">
-        <v>46251.42752314815</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>46251.427523148152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -3254,7 +3277,7 @@
         <v>793</v>
       </c>
       <c r="F5" s="1">
-        <v>46251.42914351852</v>
+        <v>46251.429143518522</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -3266,10 +3289,10 @@
         <v>796</v>
       </c>
       <c r="K5" s="1">
-        <v>46251.42917824074</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>46251.429178240738</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -3286,7 +3309,7 @@
         <v>793</v>
       </c>
       <c r="F6" s="1">
-        <v>46251.43881944445</v>
+        <v>46251.438819444447</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3298,10 +3321,10 @@
         <v>797</v>
       </c>
       <c r="K6" s="1">
-        <v>46251.44912037037</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>46251.449120370373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3318,7 +3341,7 @@
         <v>793</v>
       </c>
       <c r="F7" s="1">
-        <v>46251.45042824074</v>
+        <v>46251.450428240743</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -3330,10 +3353,10 @@
         <v>798</v>
       </c>
       <c r="K7" s="1">
-        <v>46251.45074074074</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>46251.450740740736</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -3350,7 +3373,7 @@
         <v>793</v>
       </c>
       <c r="F8" s="1">
-        <v>46251.45056712963</v>
+        <v>46251.450567129628</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3362,10 +3385,10 @@
         <v>799</v>
       </c>
       <c r="K8" s="1">
-        <v>46251.45075231481</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>46251.450752314813</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -3394,10 +3417,10 @@
         <v>800</v>
       </c>
       <c r="K9" s="1">
-        <v>46251.45077546296</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>46251.450775462959</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -3414,10 +3437,10 @@
         <v>793</v>
       </c>
       <c r="F10" s="1">
-        <v>46251.45364583333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>46251.453645833331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3434,10 +3457,10 @@
         <v>793</v>
       </c>
       <c r="F11" s="1">
-        <v>46251.45377314815</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>46251.453773148147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -3454,10 +3477,10 @@
         <v>793</v>
       </c>
       <c r="F12" s="1">
-        <v>46251.45403935185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>46251.454039351847</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -3474,7 +3497,7 @@
         <v>794</v>
       </c>
       <c r="F13" s="1">
-        <v>46251.47354166667</v>
+        <v>46251.473541666674</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3486,10 +3509,10 @@
         <v>801</v>
       </c>
       <c r="K13" s="1">
-        <v>46251.47355324074</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>46251.473553240743</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -3506,7 +3529,7 @@
         <v>793</v>
       </c>
       <c r="F14" s="1">
-        <v>46251.56199074074</v>
+        <v>46251.561990740738</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -3518,10 +3541,10 @@
         <v>802</v>
       </c>
       <c r="K14" s="1">
-        <v>46251.56201388889</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>46251.562013888892</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -3538,7 +3561,7 @@
         <v>793</v>
       </c>
       <c r="F15" s="1">
-        <v>46251.56039351852</v>
+        <v>46251.560393518521</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -3550,10 +3573,10 @@
         <v>803</v>
       </c>
       <c r="K15" s="1">
-        <v>46251.56042824074</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>46251.560428240737</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -3570,7 +3593,7 @@
         <v>794</v>
       </c>
       <c r="F16" s="1">
-        <v>46251.47449074074</v>
+        <v>46251.474490740737</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -3585,7 +3608,7 @@
         <v>46251.47451388889</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -3602,7 +3625,7 @@
         <v>793</v>
       </c>
       <c r="F17" s="1">
-        <v>46251.47466435185</v>
+        <v>46251.474664351852</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -3614,10 +3637,10 @@
         <v>805</v>
       </c>
       <c r="K17" s="1">
-        <v>46251.4746875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>46251.474687499998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -3634,7 +3657,7 @@
         <v>794</v>
       </c>
       <c r="F18" s="1">
-        <v>46251.47480324074</v>
+        <v>46251.474803240737</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -3649,7 +3672,7 @@
         <v>46251.47483796296</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -3666,10 +3689,10 @@
         <v>794</v>
       </c>
       <c r="F19" s="1">
-        <v>46251.50208333333</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>46251.502083333333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -3686,10 +3709,10 @@
         <v>793</v>
       </c>
       <c r="F20" s="1">
-        <v>46251.50223379629</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>46251.502233796287</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -3706,10 +3729,10 @@
         <v>793</v>
       </c>
       <c r="F21" s="1">
-        <v>46251.50234953704</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>46251.502349537041</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -3726,7 +3749,7 @@
         <v>794</v>
       </c>
       <c r="F22" s="1">
-        <v>46251.50628472222</v>
+        <v>46251.506284722222</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -3738,10 +3761,10 @@
         <v>807</v>
       </c>
       <c r="K22" s="1">
-        <v>46251.50631944444</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>46251.506319444437</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -3770,10 +3793,10 @@
         <v>808</v>
       </c>
       <c r="K23" s="1">
-        <v>46251.50645833334</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>46251.506458333337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -3790,7 +3813,7 @@
         <v>793</v>
       </c>
       <c r="F24" s="1">
-        <v>46251.5066087963</v>
+        <v>46251.506608796299</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3802,10 +3825,10 @@
         <v>809</v>
       </c>
       <c r="K24" s="1">
-        <v>46251.50662037037</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>46251.506620370368</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -3822,7 +3845,7 @@
         <v>793</v>
       </c>
       <c r="F25" s="1">
-        <v>46251.51034722223</v>
+        <v>46251.510347222233</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3834,10 +3857,10 @@
         <v>810</v>
       </c>
       <c r="K25" s="1">
-        <v>46251.51037037037</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>46251.510370370372</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -3854,7 +3877,7 @@
         <v>793</v>
       </c>
       <c r="F26" s="1">
-        <v>46251.56207175926</v>
+        <v>46251.562071759261</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3866,10 +3889,10 @@
         <v>811</v>
       </c>
       <c r="K26" s="1">
-        <v>46251.56209490741</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>46251.562094907407</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -3886,7 +3909,7 @@
         <v>793</v>
       </c>
       <c r="F27" s="1">
-        <v>46251.56217592592</v>
+        <v>46251.562175925923</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -3898,10 +3921,10 @@
         <v>812</v>
       </c>
       <c r="K27" s="1">
-        <v>46251.56219907408</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>46251.562199074076</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -3930,10 +3953,10 @@
         <v>813</v>
       </c>
       <c r="K28" s="1">
-        <v>46251.51087962963</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>46251.510879629634</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -3950,7 +3973,7 @@
         <v>793</v>
       </c>
       <c r="F29" s="1">
-        <v>46251.56228009259</v>
+        <v>46251.562280092592</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -3962,10 +3985,10 @@
         <v>814</v>
       </c>
       <c r="K29" s="1">
-        <v>46251.56230324074</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>46251.562303240738</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -3982,7 +4005,7 @@
         <v>793</v>
       </c>
       <c r="F30" s="1">
-        <v>46251.51162037037</v>
+        <v>46251.511620370373</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -3994,10 +4017,10 @@
         <v>815</v>
       </c>
       <c r="K30" s="1">
-        <v>46251.51164351852</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>46251.511643518519</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -4014,7 +4037,7 @@
         <v>793</v>
       </c>
       <c r="F31" s="1">
-        <v>46251.51180555556</v>
+        <v>46251.511805555558</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -4026,10 +4049,10 @@
         <v>816</v>
       </c>
       <c r="K31" s="1">
-        <v>46251.51181712963</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>46251.511817129627</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -4046,7 +4069,7 @@
         <v>793</v>
       </c>
       <c r="F32" s="1">
-        <v>46251.51197916667</v>
+        <v>46251.511979166673</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -4058,10 +4081,10 @@
         <v>817</v>
       </c>
       <c r="K32" s="1">
-        <v>46251.51200231481</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>46251.512002314812</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -4078,7 +4101,7 @@
         <v>794</v>
       </c>
       <c r="F33" s="1">
-        <v>46251.51210648148</v>
+        <v>46251.512106481481</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -4090,10 +4113,10 @@
         <v>818</v>
       </c>
       <c r="K33" s="1">
-        <v>46251.51212962963</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>46251.512129629627</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -4110,7 +4133,7 @@
         <v>793</v>
       </c>
       <c r="F34" s="1">
-        <v>46251.51224537037</v>
+        <v>46251.512245370373</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -4125,7 +4148,7 @@
         <v>46251.51226851852</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -4142,7 +4165,7 @@
         <v>794</v>
       </c>
       <c r="F35" s="1">
-        <v>46251.56237268518</v>
+        <v>46251.562372685177</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -4154,10 +4177,10 @@
         <v>820</v>
       </c>
       <c r="K35" s="1">
-        <v>46251.56238425926</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>46251.562384259261</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -4174,7 +4197,7 @@
         <v>793</v>
       </c>
       <c r="F36" s="1">
-        <v>46251.51261574074</v>
+        <v>46251.512615740743</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -4186,10 +4209,10 @@
         <v>821</v>
       </c>
       <c r="K36" s="1">
-        <v>46251.51263888889</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>46251.512638888889</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -4206,7 +4229,7 @@
         <v>793</v>
       </c>
       <c r="F37" s="1">
-        <v>46251.58087962963</v>
+        <v>46251.580879629633</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -4221,7 +4244,7 @@
         <v>46251.58090277778</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>47</v>
       </c>
@@ -4238,7 +4261,7 @@
         <v>793</v>
       </c>
       <c r="F38" s="1">
-        <v>46251.51306712963</v>
+        <v>46251.513067129628</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -4250,10 +4273,10 @@
         <v>823</v>
       </c>
       <c r="K38" s="1">
-        <v>46251.51309027777</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>46251.513090277767</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -4270,7 +4293,7 @@
         <v>793</v>
       </c>
       <c r="F39" s="1">
-        <v>46251.51318287037</v>
+        <v>46251.513182870367</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -4282,10 +4305,10 @@
         <v>824</v>
       </c>
       <c r="K39" s="1">
-        <v>46251.51320601852</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>46251.513206018521</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -4302,7 +4325,7 @@
         <v>793</v>
       </c>
       <c r="F40" s="1">
-        <v>46251.56256944445</v>
+        <v>46251.562569444453</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -4314,10 +4337,10 @@
         <v>825</v>
       </c>
       <c r="K40" s="1">
-        <v>46251.56259259259</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>46251.562592592592</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -4334,7 +4357,7 @@
         <v>794</v>
       </c>
       <c r="F41" s="1">
-        <v>46251.56266203704</v>
+        <v>46251.562662037039</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -4346,10 +4369,10 @@
         <v>826</v>
       </c>
       <c r="K41" s="1">
-        <v>46251.56267361111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>46251.562673611108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -4366,7 +4389,7 @@
         <v>793</v>
       </c>
       <c r="F42" s="1">
-        <v>46251.51365740741</v>
+        <v>46251.513657407413</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -4378,10 +4401,10 @@
         <v>827</v>
       </c>
       <c r="K42" s="1">
-        <v>46251.51368055555</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>46251.513680555552</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>52</v>
       </c>
@@ -4398,7 +4421,7 @@
         <v>793</v>
       </c>
       <c r="F43" s="1">
-        <v>46251.56274305555</v>
+        <v>46251.562743055547</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -4410,10 +4433,10 @@
         <v>828</v>
       </c>
       <c r="K43" s="1">
-        <v>46251.56278935185</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>46251.562789351847</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -4430,7 +4453,7 @@
         <v>793</v>
       </c>
       <c r="F44" s="1">
-        <v>46251.56285879629</v>
+        <v>46251.562858796293</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -4442,10 +4465,10 @@
         <v>829</v>
       </c>
       <c r="K44" s="1">
-        <v>46251.56288194445</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>46251.562881944446</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>54</v>
       </c>
@@ -4474,10 +4497,10 @@
         <v>830</v>
       </c>
       <c r="K45" s="1">
-        <v>46251.51428240741</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>46251.514282407406</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -4494,7 +4517,7 @@
         <v>793</v>
       </c>
       <c r="F46" s="1">
-        <v>46251.51440972222</v>
+        <v>46251.514409722222</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -4506,10 +4529,10 @@
         <v>831</v>
       </c>
       <c r="K46" s="1">
-        <v>46251.51443287037</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>46251.514432870368</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -4526,7 +4549,7 @@
         <v>793</v>
       </c>
       <c r="F47" s="1">
-        <v>46251.51452546296</v>
+        <v>46251.514525462961</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -4538,10 +4561,10 @@
         <v>832</v>
       </c>
       <c r="K47" s="1">
-        <v>46251.51453703704</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>46251.514537037037</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -4558,7 +4581,7 @@
         <v>793</v>
       </c>
       <c r="F48" s="1">
-        <v>46251.51465277778</v>
+        <v>46251.514652777783</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -4570,10 +4593,10 @@
         <v>833</v>
       </c>
       <c r="K48" s="1">
-        <v>46251.51467592592</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>46251.514675925922</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -4590,7 +4613,7 @@
         <v>793</v>
       </c>
       <c r="F49" s="1">
-        <v>46251.51479166667</v>
+        <v>46251.514791666668</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -4602,10 +4625,10 @@
         <v>834</v>
       </c>
       <c r="K49" s="1">
-        <v>46251.51481481481</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>46251.514814814807</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -4622,7 +4645,7 @@
         <v>793</v>
       </c>
       <c r="F50" s="1">
-        <v>46251.51493055555</v>
+        <v>46251.514930555553</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -4637,7 +4660,7 @@
         <v>46251.51494212963</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -4654,7 +4677,7 @@
         <v>794</v>
       </c>
       <c r="F51" s="1">
-        <v>46251.51509259259</v>
+        <v>46251.515092592592</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -4666,10 +4689,10 @@
         <v>836</v>
       </c>
       <c r="K51" s="1">
-        <v>46251.51512731481</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>46251.515127314808</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -4686,7 +4709,7 @@
         <v>793</v>
       </c>
       <c r="F52" s="1">
-        <v>46251.51526620371</v>
+        <v>46251.515266203707</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -4698,10 +4721,10 @@
         <v>837</v>
       </c>
       <c r="K52" s="1">
-        <v>46251.51528935185</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>46251.515289351853</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>62</v>
       </c>
@@ -4718,7 +4741,7 @@
         <v>793</v>
       </c>
       <c r="F53" s="1">
-        <v>46251.51543981482</v>
+        <v>46251.515439814822</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -4730,10 +4753,10 @@
         <v>838</v>
       </c>
       <c r="K53" s="1">
-        <v>46251.51545138889</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>46251.515451388892</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -4750,7 +4773,7 @@
         <v>793</v>
       </c>
       <c r="F54" s="1">
-        <v>46251.56296296296</v>
+        <v>46251.562962962962</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -4762,10 +4785,10 @@
         <v>839</v>
       </c>
       <c r="K54" s="1">
-        <v>46251.56297453704</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>46251.562974537039</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>64</v>
       </c>
@@ -4782,7 +4805,7 @@
         <v>794</v>
       </c>
       <c r="F55" s="1">
-        <v>46251.51575231482</v>
+        <v>46251.515752314823</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -4794,10 +4817,10 @@
         <v>840</v>
       </c>
       <c r="K55" s="1">
-        <v>46251.51576388889</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>46251.515763888892</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -4814,7 +4837,7 @@
         <v>793</v>
       </c>
       <c r="F56" s="1">
-        <v>46251.51592592592</v>
+        <v>46251.515925925924</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -4826,10 +4849,10 @@
         <v>841</v>
       </c>
       <c r="K56" s="1">
-        <v>46251.51594907408</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>46251.515949074077</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -4846,7 +4869,7 @@
         <v>793</v>
       </c>
       <c r="F57" s="1">
-        <v>46251.51605324074</v>
+        <v>46251.516053240739</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -4858,10 +4881,10 @@
         <v>842</v>
       </c>
       <c r="K57" s="1">
-        <v>46251.51607638889</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>46251.516076388893</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -4878,7 +4901,7 @@
         <v>793</v>
       </c>
       <c r="F58" s="1">
-        <v>46251.51628472222</v>
+        <v>46251.516284722216</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -4893,7 +4916,7 @@
         <v>46251.51630787037</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -4910,7 +4933,7 @@
         <v>793</v>
       </c>
       <c r="F59" s="1">
-        <v>46251.51640046296</v>
+        <v>46251.516400462962</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -4922,10 +4945,10 @@
         <v>844</v>
       </c>
       <c r="K59" s="1">
-        <v>46251.51641203704</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>46251.516412037039</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -4942,7 +4965,7 @@
         <v>793</v>
       </c>
       <c r="F60" s="1">
-        <v>46251.51663194445</v>
+        <v>46251.516631944447</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -4954,10 +4977,10 @@
         <v>845</v>
       </c>
       <c r="K60" s="1">
-        <v>46251.51665509259</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>46251.516655092593</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -4974,7 +4997,7 @@
         <v>794</v>
       </c>
       <c r="F61" s="1">
-        <v>46251.51678240741</v>
+        <v>46251.516782407409</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -4986,10 +5009,10 @@
         <v>846</v>
       </c>
       <c r="K61" s="1">
-        <v>46251.51680555556</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>46251.516805555562</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -5006,7 +5029,7 @@
         <v>793</v>
       </c>
       <c r="F62" s="1">
-        <v>46251.56305555555</v>
+        <v>46251.563055555547</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -5018,10 +5041,10 @@
         <v>847</v>
       </c>
       <c r="K62" s="1">
-        <v>46251.56306712963</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>46251.563067129631</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>72</v>
       </c>
@@ -5038,7 +5061,7 @@
         <v>793</v>
       </c>
       <c r="F63" s="1">
-        <v>46251.58074074074</v>
+        <v>46251.580740740741</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -5050,10 +5073,10 @@
         <v>848</v>
       </c>
       <c r="K63" s="1">
-        <v>46251.58078703703</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>46251.580787037034</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -5070,7 +5093,7 @@
         <v>793</v>
       </c>
       <c r="F64" s="1">
-        <v>46251.51756944445</v>
+        <v>46251.517569444448</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -5082,10 +5105,10 @@
         <v>849</v>
       </c>
       <c r="K64" s="1">
-        <v>46251.51759259259</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>46251.517592592587</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -5102,7 +5125,7 @@
         <v>793</v>
       </c>
       <c r="F65" s="1">
-        <v>46251.51768518519</v>
+        <v>46251.517685185187</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -5114,10 +5137,10 @@
         <v>850</v>
       </c>
       <c r="K65" s="1">
-        <v>46251.51769675926</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+        <v>46251.517696759263</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>75</v>
       </c>
@@ -5134,7 +5157,7 @@
         <v>793</v>
       </c>
       <c r="F66" s="1">
-        <v>46251.51778935185</v>
+        <v>46251.517789351848</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -5146,10 +5169,10 @@
         <v>851</v>
       </c>
       <c r="K66" s="1">
-        <v>46251.5178125</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+        <v>46251.517812500002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>76</v>
       </c>
@@ -5166,7 +5189,7 @@
         <v>793</v>
       </c>
       <c r="F67" s="1">
-        <v>46251.51795138889</v>
+        <v>46251.517951388887</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -5178,10 +5201,10 @@
         <v>852</v>
       </c>
       <c r="K67" s="1">
-        <v>46251.51797453704</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
+        <v>46251.517974537041</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -5198,7 +5221,7 @@
         <v>793</v>
       </c>
       <c r="F68" s="1">
-        <v>46251.51814814815</v>
+        <v>46251.518148148149</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -5210,10 +5233,10 @@
         <v>853</v>
       </c>
       <c r="K68" s="1">
-        <v>46251.51817129629</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
+        <v>46251.518171296288</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -5230,7 +5253,7 @@
         <v>793</v>
       </c>
       <c r="F69" s="1">
-        <v>46251.51831018519</v>
+        <v>46251.518310185187</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -5245,7 +5268,7 @@
         <v>46251.51834490741</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -5262,7 +5285,7 @@
         <v>793</v>
       </c>
       <c r="F70" s="1">
-        <v>46251.51846064815</v>
+        <v>46251.518460648149</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -5274,10 +5297,10 @@
         <v>855</v>
       </c>
       <c r="K70" s="1">
-        <v>46251.5184837963</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+        <v>46251.518483796302</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -5294,7 +5317,7 @@
         <v>793</v>
       </c>
       <c r="F71" s="1">
-        <v>46251.51859953703</v>
+        <v>46251.518599537027</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -5306,10 +5329,10 @@
         <v>856</v>
       </c>
       <c r="K71" s="1">
-        <v>46251.51862268519</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
+        <v>46251.518622685187</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -5326,7 +5349,7 @@
         <v>793</v>
       </c>
       <c r="F72" s="1">
-        <v>46251.51881944444</v>
+        <v>46251.518819444442</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -5338,10 +5361,10 @@
         <v>857</v>
       </c>
       <c r="K72" s="1">
-        <v>46251.51883101852</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
+        <v>46251.518831018519</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -5358,7 +5381,7 @@
         <v>793</v>
       </c>
       <c r="F73" s="1">
-        <v>46251.5190162037</v>
+        <v>46251.519016203703</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -5370,10 +5393,10 @@
         <v>858</v>
       </c>
       <c r="K73" s="1">
-        <v>46251.51905092593</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
+        <v>46251.519050925926</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -5390,7 +5413,7 @@
         <v>793</v>
       </c>
       <c r="F74" s="1">
-        <v>46251.51922453703</v>
+        <v>46251.519224537027</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -5402,10 +5425,10 @@
         <v>859</v>
       </c>
       <c r="K74" s="1">
-        <v>46251.51924768519</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
+        <v>46251.519247685188</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -5437,7 +5460,7 @@
         <v>46251.51935185185</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -5454,7 +5477,7 @@
         <v>793</v>
       </c>
       <c r="F76" s="1">
-        <v>46251.51953703703</v>
+        <v>46251.519537037027</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -5466,10 +5489,10 @@
         <v>861</v>
       </c>
       <c r="K76" s="1">
-        <v>46251.51954861111</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+        <v>46251.519548611112</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -5486,7 +5509,7 @@
         <v>793</v>
       </c>
       <c r="F77" s="1">
-        <v>46251.51969907407</v>
+        <v>46251.519699074073</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -5501,7 +5524,7 @@
         <v>46251.51972222222</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -5518,7 +5541,7 @@
         <v>793</v>
       </c>
       <c r="F78" s="1">
-        <v>46251.56321759259</v>
+        <v>46251.563217592593</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -5530,10 +5553,10 @@
         <v>863</v>
       </c>
       <c r="K78" s="1">
-        <v>46251.56324074074</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+        <v>46251.563240740739</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -5562,10 +5585,10 @@
         <v>864</v>
       </c>
       <c r="K79" s="1">
-        <v>46251.5200462963</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
+        <v>46251.520046296297</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -5582,7 +5605,7 @@
         <v>793</v>
       </c>
       <c r="F80" s="1">
-        <v>46251.52013888889</v>
+        <v>46251.520138888889</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -5594,10 +5617,10 @@
         <v>865</v>
       </c>
       <c r="K80" s="1">
-        <v>46251.52015046297</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
+        <v>46251.520150462973</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>90</v>
       </c>
@@ -5614,7 +5637,7 @@
         <v>794</v>
       </c>
       <c r="F81" s="1">
-        <v>46251.52030092593</v>
+        <v>46251.520300925928</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -5626,10 +5649,10 @@
         <v>866</v>
       </c>
       <c r="K81" s="1">
-        <v>46251.52032407407</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
+        <v>46251.520324074067</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>91</v>
       </c>
@@ -5646,7 +5669,7 @@
         <v>793</v>
       </c>
       <c r="F82" s="1">
-        <v>46251.52046296297</v>
+        <v>46251.520462962973</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -5658,10 +5681,10 @@
         <v>867</v>
       </c>
       <c r="K82" s="1">
-        <v>46251.52047453704</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
+        <v>46251.520474537043</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -5678,7 +5701,7 @@
         <v>793</v>
       </c>
       <c r="F83" s="1">
-        <v>46251.56329861111</v>
+        <v>46251.563298611109</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -5690,10 +5713,10 @@
         <v>868</v>
       </c>
       <c r="K83" s="1">
-        <v>46251.56332175926</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
+        <v>46251.563321759262</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>93</v>
       </c>
@@ -5710,7 +5733,7 @@
         <v>793</v>
       </c>
       <c r="F84" s="1">
-        <v>46251.56340277778</v>
+        <v>46251.563402777778</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -5722,10 +5745,10 @@
         <v>869</v>
       </c>
       <c r="K84" s="1">
-        <v>46251.56342592592</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
+        <v>46251.563425925917</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -5754,10 +5777,10 @@
         <v>870</v>
       </c>
       <c r="K85" s="1">
-        <v>46251.56351851852</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
+        <v>46251.563518518517</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>95</v>
       </c>
@@ -5774,7 +5797,7 @@
         <v>793</v>
       </c>
       <c r="F86" s="1">
-        <v>46251.52104166667</v>
+        <v>46251.521041666667</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -5786,10 +5809,10 @@
         <v>871</v>
       </c>
       <c r="K86" s="1">
-        <v>46251.52105324074</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
+        <v>46251.521053240736</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>96</v>
       </c>
@@ -5806,7 +5829,7 @@
         <v>794</v>
       </c>
       <c r="F87" s="1">
-        <v>46251.56359953704</v>
+        <v>46251.563599537039</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -5818,10 +5841,10 @@
         <v>872</v>
       </c>
       <c r="K87" s="1">
-        <v>46251.56361111111</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
+        <v>46251.563611111109</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>97</v>
       </c>
@@ -5838,7 +5861,7 @@
         <v>793</v>
       </c>
       <c r="F88" s="1">
-        <v>46251.52137731481</v>
+        <v>46251.521377314813</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -5853,7 +5876,7 @@
         <v>46251.52140046296</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>98</v>
       </c>
@@ -5870,7 +5893,7 @@
         <v>793</v>
       </c>
       <c r="F89" s="1">
-        <v>46251.5215625</v>
+        <v>46251.521562499998</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -5882,10 +5905,10 @@
         <v>874</v>
       </c>
       <c r="K89" s="1">
-        <v>46251.52158564814</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
+        <v>46251.521585648137</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -5902,7 +5925,7 @@
         <v>793</v>
       </c>
       <c r="F90" s="1">
-        <v>46251.52172453704</v>
+        <v>46251.521724537037</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -5914,10 +5937,10 @@
         <v>875</v>
       </c>
       <c r="K90" s="1">
-        <v>46251.52174768518</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
+        <v>46251.521747685183</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>100</v>
       </c>
@@ -5934,7 +5957,7 @@
         <v>793</v>
       </c>
       <c r="F91" s="1">
-        <v>46251.52184027778</v>
+        <v>46251.521840277783</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -5946,10 +5969,10 @@
         <v>876</v>
       </c>
       <c r="K91" s="1">
-        <v>46251.52186342593</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
+        <v>46251.521863425929</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>101</v>
       </c>
@@ -5966,7 +5989,7 @@
         <v>793</v>
       </c>
       <c r="F92" s="1">
-        <v>46251.52199074074</v>
+        <v>46251.521990740737</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -5978,10 +6001,10 @@
         <v>877</v>
       </c>
       <c r="K92" s="1">
-        <v>46251.52201388889</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
+        <v>46251.522013888891</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>102</v>
       </c>
@@ -5998,7 +6021,7 @@
         <v>793</v>
       </c>
       <c r="F93" s="1">
-        <v>46251.52217592593</v>
+        <v>46251.522175925929</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -6010,10 +6033,10 @@
         <v>878</v>
       </c>
       <c r="K93" s="1">
-        <v>46251.5221875</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
+        <v>46251.522187499999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>103</v>
       </c>
@@ -6030,7 +6053,7 @@
         <v>793</v>
       </c>
       <c r="F94" s="1">
-        <v>46251.52234953704</v>
+        <v>46251.522349537037</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -6042,10 +6065,10 @@
         <v>879</v>
       </c>
       <c r="K94" s="1">
-        <v>46251.52237268518</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
+        <v>46251.522372685176</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -6062,7 +6085,7 @@
         <v>793</v>
       </c>
       <c r="F95" s="1">
-        <v>46251.56368055556</v>
+        <v>46251.563680555562</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -6074,10 +6097,10 @@
         <v>880</v>
       </c>
       <c r="K95" s="1">
-        <v>46251.5637037037</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
+        <v>46251.563703703701</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>105</v>
       </c>
@@ -6094,7 +6117,7 @@
         <v>793</v>
       </c>
       <c r="F96" s="1">
-        <v>46251.52266203704</v>
+        <v>46251.522662037038</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -6109,7 +6132,7 @@
         <v>46251.52270833333</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>106</v>
       </c>
@@ -6126,7 +6149,7 @@
         <v>794</v>
       </c>
       <c r="F97" s="1">
-        <v>46251.52288194445</v>
+        <v>46251.522881944453</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -6138,10 +6161,10 @@
         <v>882</v>
       </c>
       <c r="K97" s="1">
-        <v>46251.52290509259</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11">
+        <v>46251.522905092592</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -6158,7 +6181,7 @@
         <v>793</v>
       </c>
       <c r="F98" s="1">
-        <v>46251.52299768518</v>
+        <v>46251.522997685177</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6170,10 +6193,10 @@
         <v>883</v>
       </c>
       <c r="K98" s="1">
-        <v>46251.52302083333</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
+        <v>46251.523020833331</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>108</v>
       </c>
@@ -6190,7 +6213,7 @@
         <v>793</v>
       </c>
       <c r="F99" s="1">
-        <v>46251.52311342592</v>
+        <v>46251.523113425923</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -6205,7 +6228,7 @@
         <v>46251.523125</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>109</v>
       </c>
@@ -6222,7 +6245,7 @@
         <v>793</v>
       </c>
       <c r="F100" s="1">
-        <v>46251.52324074074</v>
+        <v>46251.523240740738</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -6234,10 +6257,10 @@
         <v>885</v>
       </c>
       <c r="K100" s="1">
-        <v>46251.52326388889</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
+        <v>46251.523263888892</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>110</v>
       </c>
@@ -6254,7 +6277,7 @@
         <v>793</v>
       </c>
       <c r="F101" s="1">
-        <v>46251.52337962963</v>
+        <v>46251.523379629631</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -6266,10 +6289,10 @@
         <v>886</v>
       </c>
       <c r="K101" s="1">
-        <v>46251.52340277778</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11">
+        <v>46251.523402777777</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>111</v>
       </c>
@@ -6286,7 +6309,7 @@
         <v>794</v>
       </c>
       <c r="F102" s="1">
-        <v>46251.52354166667</v>
+        <v>46251.523541666669</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -6298,10 +6321,10 @@
         <v>887</v>
       </c>
       <c r="K102" s="1">
-        <v>46251.52356481482</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11">
+        <v>46251.523564814823</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>112</v>
       </c>
@@ -6318,7 +6341,7 @@
         <v>794</v>
       </c>
       <c r="F103" s="1">
-        <v>46251.52368055555</v>
+        <v>46251.523680555547</v>
       </c>
       <c r="H103">
         <v>0</v>
@@ -6333,7 +6356,7 @@
         <v>46251.5237037037</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>113</v>
       </c>
@@ -6350,7 +6373,7 @@
         <v>793</v>
       </c>
       <c r="F104" s="1">
-        <v>46251.52383101852</v>
+        <v>46251.523831018523</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -6362,10 +6385,10 @@
         <v>889</v>
       </c>
       <c r="K104" s="1">
-        <v>46251.52384259259</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11">
+        <v>46251.523842592593</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>114</v>
       </c>
@@ -6382,7 +6405,7 @@
         <v>794</v>
       </c>
       <c r="F105" s="1">
-        <v>46251.52393518519</v>
+        <v>46251.523935185192</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -6394,10 +6417,10 @@
         <v>890</v>
       </c>
       <c r="K105" s="1">
-        <v>46251.52395833333</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11">
+        <v>46251.523958333331</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>115</v>
       </c>
@@ -6414,7 +6437,7 @@
         <v>793</v>
       </c>
       <c r="F106" s="1">
-        <v>46251.5240625</v>
+        <v>46251.524062500001</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -6426,10 +6449,10 @@
         <v>891</v>
       </c>
       <c r="K106" s="1">
-        <v>46251.52408564815</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11">
+        <v>46251.524085648147</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>116</v>
       </c>
@@ -6446,7 +6469,7 @@
         <v>793</v>
       </c>
       <c r="F107" s="1">
-        <v>46251.52421296296</v>
+        <v>46251.524212962962</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -6458,10 +6481,10 @@
         <v>892</v>
       </c>
       <c r="K107" s="1">
-        <v>46251.52424768519</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11">
+        <v>46251.524247685193</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>117</v>
       </c>
@@ -6478,7 +6501,7 @@
         <v>793</v>
       </c>
       <c r="F108" s="1">
-        <v>46251.52434027778</v>
+        <v>46251.524340277778</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -6490,10 +6513,10 @@
         <v>893</v>
       </c>
       <c r="K108" s="1">
-        <v>46251.52436342592</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11">
+        <v>46251.524363425917</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>118</v>
       </c>
@@ -6510,7 +6533,7 @@
         <v>794</v>
       </c>
       <c r="F109" s="1">
-        <v>46251.52446759259</v>
+        <v>46251.524467592593</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -6522,10 +6545,10 @@
         <v>894</v>
       </c>
       <c r="K109" s="1">
-        <v>46251.52450231482</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11">
+        <v>46251.524502314824</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>119</v>
       </c>
@@ -6542,7 +6565,7 @@
         <v>793</v>
       </c>
       <c r="F110" s="1">
-        <v>46251.52462962963</v>
+        <v>46251.524629629632</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -6554,10 +6577,10 @@
         <v>895</v>
       </c>
       <c r="K110" s="1">
-        <v>46251.52465277778</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11">
+        <v>46251.524652777778</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>120</v>
       </c>
@@ -6574,7 +6597,7 @@
         <v>793</v>
       </c>
       <c r="F111" s="1">
-        <v>46251.52479166666</v>
+        <v>46251.524791666663</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -6586,10 +6609,10 @@
         <v>896</v>
       </c>
       <c r="K111" s="1">
-        <v>46251.52481481482</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
+        <v>46251.524814814817</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>121</v>
       </c>
@@ -6606,7 +6629,7 @@
         <v>793</v>
       </c>
       <c r="F112" s="1">
-        <v>46251.52508101852</v>
+        <v>46251.525081018517</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -6618,10 +6641,10 @@
         <v>897</v>
       </c>
       <c r="K112" s="1">
-        <v>46251.52510416666</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
+        <v>46251.525104166663</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>122</v>
       </c>
@@ -6638,7 +6661,7 @@
         <v>793</v>
       </c>
       <c r="F113" s="1">
-        <v>46251.56377314815</v>
+        <v>46251.563773148147</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -6650,10 +6673,10 @@
         <v>898</v>
       </c>
       <c r="K113" s="1">
-        <v>46251.56380787037</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
+        <v>46251.563807870371</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>123</v>
       </c>
@@ -6670,7 +6693,7 @@
         <v>794</v>
       </c>
       <c r="F114" s="1">
-        <v>46251.52537037037</v>
+        <v>46251.525370370371</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -6682,10 +6705,10 @@
         <v>899</v>
       </c>
       <c r="K114" s="1">
-        <v>46251.52539351852</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
+        <v>46251.525393518517</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>124</v>
       </c>
@@ -6714,10 +6737,10 @@
         <v>900</v>
       </c>
       <c r="K115" s="1">
-        <v>46251.52555555556</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
+        <v>46251.525555555563</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>125</v>
       </c>
@@ -6734,7 +6757,7 @@
         <v>793</v>
       </c>
       <c r="F116" s="1">
-        <v>46251.52568287037</v>
+        <v>46251.525682870371</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -6746,10 +6769,10 @@
         <v>901</v>
       </c>
       <c r="K116" s="1">
-        <v>46251.52569444444</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11">
+        <v>46251.525694444441</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>126</v>
       </c>
@@ -6766,7 +6789,7 @@
         <v>794</v>
       </c>
       <c r="F117" s="1">
-        <v>46251.52583333333</v>
+        <v>46251.525833333333</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -6778,10 +6801,10 @@
         <v>902</v>
       </c>
       <c r="K117" s="1">
-        <v>46251.52585648148</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
+        <v>46251.525856481479</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>127</v>
       </c>
@@ -6798,7 +6821,7 @@
         <v>793</v>
       </c>
       <c r="F118" s="1">
-        <v>46251.52604166666</v>
+        <v>46251.526041666657</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -6810,10 +6833,10 @@
         <v>903</v>
       </c>
       <c r="K118" s="1">
-        <v>46251.52606481482</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
+        <v>46251.526064814818</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>128</v>
       </c>
@@ -6830,7 +6853,7 @@
         <v>793</v>
       </c>
       <c r="F119" s="1">
-        <v>46251.52619212963</v>
+        <v>46251.526192129633</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -6845,7 +6868,7 @@
         <v>46251.52621527778</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>129</v>
       </c>
@@ -6862,7 +6885,7 @@
         <v>793</v>
       </c>
       <c r="F120" s="1">
-        <v>46251.5263425926</v>
+        <v>46251.526342592602</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -6874,10 +6897,10 @@
         <v>905</v>
       </c>
       <c r="K120" s="1">
-        <v>46251.52636574074</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
+        <v>46251.526365740741</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>130</v>
       </c>
@@ -6894,7 +6917,7 @@
         <v>793</v>
       </c>
       <c r="F121" s="1">
-        <v>46251.52646990741</v>
+        <v>46251.526469907411</v>
       </c>
       <c r="H121">
         <v>0</v>
@@ -6906,10 +6929,10 @@
         <v>906</v>
       </c>
       <c r="K121" s="1">
-        <v>46251.52649305556</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
+        <v>46251.526493055557</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>131</v>
       </c>
@@ -6926,7 +6949,7 @@
         <v>794</v>
       </c>
       <c r="F122" s="1">
-        <v>46251.52663194444</v>
+        <v>46251.526631944442</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -6938,10 +6961,10 @@
         <v>907</v>
       </c>
       <c r="K122" s="1">
-        <v>46251.5266550926</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11">
+        <v>46251.526655092603</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>132</v>
       </c>
@@ -6958,7 +6981,7 @@
         <v>794</v>
       </c>
       <c r="F123" s="1">
-        <v>46251.52680555556</v>
+        <v>46251.526805555557</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -6970,10 +6993,10 @@
         <v>908</v>
       </c>
       <c r="K123" s="1">
-        <v>46251.52681712963</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
+        <v>46251.526817129627</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>133</v>
       </c>
@@ -6990,7 +7013,7 @@
         <v>793</v>
       </c>
       <c r="F124" s="1">
-        <v>46251.52697916667</v>
+        <v>46251.526979166672</v>
       </c>
       <c r="H124">
         <v>0</v>
@@ -7002,10 +7025,10 @@
         <v>909</v>
       </c>
       <c r="K124" s="1">
-        <v>46251.52699074074</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
+        <v>46251.526990740742</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>134</v>
       </c>
@@ -7022,7 +7045,7 @@
         <v>793</v>
       </c>
       <c r="F125" s="1">
-        <v>46251.52711805556</v>
+        <v>46251.527118055557</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -7034,10 +7057,10 @@
         <v>910</v>
       </c>
       <c r="K125" s="1">
-        <v>46251.5271412037</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
+        <v>46251.527141203696</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>135</v>
       </c>
@@ -7054,7 +7077,7 @@
         <v>793</v>
       </c>
       <c r="F126" s="1">
-        <v>46251.52722222222</v>
+        <v>46251.527222222219</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -7066,10 +7089,10 @@
         <v>911</v>
       </c>
       <c r="K126" s="1">
-        <v>46251.52724537037</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
+        <v>46251.527245370373</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>136</v>
       </c>
@@ -7086,7 +7109,7 @@
         <v>793</v>
       </c>
       <c r="F127" s="1">
-        <v>46251.52737268519</v>
+        <v>46251.527372685188</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -7098,10 +7121,10 @@
         <v>912</v>
       </c>
       <c r="K127" s="1">
-        <v>46251.52739583333</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
+        <v>46251.527395833327</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>137</v>
       </c>
@@ -7130,10 +7153,10 @@
         <v>913</v>
       </c>
       <c r="K128" s="1">
-        <v>46251.52756944444</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11">
+        <v>46251.527569444443</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>138</v>
       </c>
@@ -7162,10 +7185,10 @@
         <v>914</v>
       </c>
       <c r="K129" s="1">
-        <v>46251.56390046296</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11">
+        <v>46251.563900462963</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>139</v>
       </c>
@@ -7182,7 +7205,7 @@
         <v>793</v>
       </c>
       <c r="F130" s="1">
-        <v>46251.53675925926</v>
+        <v>46251.536759259259</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -7194,10 +7217,10 @@
         <v>915</v>
       </c>
       <c r="K130" s="1">
-        <v>46251.53678240741</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11">
+        <v>46251.536782407413</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>140</v>
       </c>
@@ -7214,7 +7237,7 @@
         <v>793</v>
       </c>
       <c r="F131" s="1">
-        <v>46251.53689814815</v>
+        <v>46251.536898148152</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -7226,10 +7249,10 @@
         <v>916</v>
       </c>
       <c r="K131" s="1">
-        <v>46251.5369212963</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11">
+        <v>46251.536921296298</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>141</v>
       </c>
@@ -7246,7 +7269,7 @@
         <v>793</v>
       </c>
       <c r="F132" s="1">
-        <v>46251.53706018518</v>
+        <v>46251.537060185183</v>
       </c>
       <c r="H132">
         <v>0</v>
@@ -7258,10 +7281,10 @@
         <v>917</v>
       </c>
       <c r="K132" s="1">
-        <v>46251.53709490741</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11">
+        <v>46251.537094907413</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>142</v>
       </c>
@@ -7278,7 +7301,7 @@
         <v>793</v>
       </c>
       <c r="F133" s="1">
-        <v>46251.54084490741</v>
+        <v>46251.540844907409</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -7290,10 +7313,10 @@
         <v>918</v>
       </c>
       <c r="K133" s="1">
-        <v>46251.54087962963</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11">
+        <v>46251.540879629632</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>143</v>
       </c>
@@ -7310,7 +7333,7 @@
         <v>794</v>
       </c>
       <c r="F134" s="1">
-        <v>46251.56396990741</v>
+        <v>46251.563969907409</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -7322,10 +7345,10 @@
         <v>919</v>
       </c>
       <c r="K134" s="1">
-        <v>46251.56399305556</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11">
+        <v>46251.563993055563</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>144</v>
       </c>
@@ -7342,7 +7365,7 @@
         <v>793</v>
       </c>
       <c r="F135" s="1">
-        <v>46251.54581018518</v>
+        <v>46251.545810185176</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -7357,7 +7380,7 @@
         <v>46251.54583333333</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>145</v>
       </c>
@@ -7374,7 +7397,7 @@
         <v>793</v>
       </c>
       <c r="F136" s="1">
-        <v>46251.55112268519</v>
+        <v>46251.551122685189</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -7386,10 +7409,10 @@
         <v>921</v>
       </c>
       <c r="K136" s="1">
-        <v>46251.5511574074</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11">
+        <v>46251.551157407397</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>146</v>
       </c>
@@ -7406,7 +7429,7 @@
         <v>793</v>
       </c>
       <c r="F137" s="1">
-        <v>46251.57864583333</v>
+        <v>46251.578645833331</v>
       </c>
       <c r="H137">
         <v>1</v>
@@ -7418,10 +7441,10 @@
         <v>922</v>
       </c>
       <c r="K137" s="1">
-        <v>46251.57866898148</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11">
+        <v>46251.578668981478</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>147</v>
       </c>
@@ -7438,9 +7461,9 @@
         <v>793</v>
       </c>
       <c r="F138" s="1">
-        <v>46251.59761574074</v>
-      </c>
-      <c r="H138" t="b">
+        <v>46251.597615740742</v>
+      </c>
+      <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
@@ -7450,10 +7473,10 @@
         <v>923</v>
       </c>
       <c r="K138" s="1">
-        <v>46251.59763888889</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11">
+        <v>46251.597638888888</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>148</v>
       </c>
@@ -7470,7 +7493,7 @@
         <v>793</v>
       </c>
       <c r="F139" s="1">
-        <v>46251.58373842593</v>
+        <v>46251.583738425928</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -7482,10 +7505,10 @@
         <v>924</v>
       </c>
       <c r="K139" s="1">
-        <v>46251.58378472222</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11">
+        <v>46251.583784722221</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>149</v>
       </c>
@@ -7502,7 +7525,7 @@
         <v>793</v>
       </c>
       <c r="F140" s="1">
-        <v>46251.58387731481</v>
+        <v>46251.583877314813</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -7517,7 +7540,7 @@
         <v>46251.58390046296</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>150</v>
       </c>
@@ -7534,7 +7557,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>151</v>
       </c>
@@ -7551,7 +7574,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>152</v>
       </c>
@@ -7568,7 +7591,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>153</v>
       </c>
@@ -7585,7 +7608,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>154</v>
       </c>
@@ -7602,7 +7625,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>155</v>
       </c>
@@ -7619,7 +7642,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>156</v>
       </c>
@@ -7636,7 +7659,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>157</v>
       </c>
@@ -7653,7 +7676,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>158</v>
       </c>
@@ -7670,7 +7693,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>159</v>
       </c>
@@ -7687,7 +7710,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>160</v>
       </c>
@@ -7704,7 +7727,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>161</v>
       </c>
@@ -7721,7 +7744,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>162</v>
       </c>
@@ -7738,7 +7761,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>163</v>
       </c>
@@ -7755,7 +7778,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>164</v>
       </c>
@@ -7772,7 +7795,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>165</v>
       </c>
@@ -7789,7 +7812,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>166</v>
       </c>
@@ -7806,7 +7829,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>167</v>
       </c>
@@ -7823,7 +7846,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>168</v>
       </c>
@@ -7840,7 +7863,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>169</v>
       </c>
@@ -7857,7 +7880,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>170</v>
       </c>
@@ -7874,7 +7897,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>171</v>
       </c>
@@ -7891,7 +7914,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>172</v>
       </c>
@@ -7908,7 +7931,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>173</v>
       </c>
@@ -7925,7 +7948,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>174</v>
       </c>
@@ -7942,7 +7965,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>175</v>
       </c>
@@ -7959,7 +7982,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>176</v>
       </c>
@@ -7976,7 +7999,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>177</v>
       </c>
@@ -7993,7 +8016,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>178</v>
       </c>
@@ -8010,7 +8033,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>179</v>
       </c>
@@ -8027,7 +8050,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>180</v>
       </c>
@@ -8044,7 +8067,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>181</v>
       </c>
@@ -8061,7 +8084,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>182</v>
       </c>
@@ -8078,7 +8101,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>183</v>
       </c>
@@ -8095,7 +8118,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>184</v>
       </c>
@@ -8112,7 +8135,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>185</v>
       </c>
@@ -8129,7 +8152,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>186</v>
       </c>
@@ -8146,7 +8169,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>187</v>
       </c>
@@ -8163,7 +8186,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>188</v>
       </c>
@@ -8180,7 +8203,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>189</v>
       </c>
@@ -8197,7 +8220,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>190</v>
       </c>
@@ -8214,7 +8237,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>191</v>
       </c>
@@ -8231,7 +8254,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>192</v>
       </c>
@@ -8248,7 +8271,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>193</v>
       </c>
@@ -8265,7 +8288,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>194</v>
       </c>
@@ -8282,7 +8305,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>195</v>
       </c>
@@ -8299,7 +8322,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>196</v>
       </c>
@@ -8316,7 +8339,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>197</v>
       </c>
@@ -8333,7 +8356,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>198</v>
       </c>
@@ -8350,7 +8373,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>199</v>
       </c>
@@ -8367,7 +8390,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>200</v>
       </c>
@@ -8384,7 +8407,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>201</v>
       </c>
@@ -8401,7 +8424,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>202</v>
       </c>
@@ -8418,7 +8441,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>203</v>
       </c>
@@ -8435,7 +8458,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>204</v>
       </c>
@@ -8452,7 +8475,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>205</v>
       </c>
@@ -8469,7 +8492,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>206</v>
       </c>
@@ -8486,7 +8509,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>207</v>
       </c>
@@ -8503,7 +8526,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>208</v>
       </c>
@@ -8520,7 +8543,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>209</v>
       </c>
@@ -8537,7 +8560,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>210</v>
       </c>
@@ -8554,7 +8577,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>211</v>
       </c>
@@ -8571,7 +8594,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>212</v>
       </c>
@@ -8588,7 +8611,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>213</v>
       </c>
@@ -8605,7 +8628,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>214</v>
       </c>
@@ -8622,7 +8645,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>215</v>
       </c>
@@ -8639,7 +8662,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>216</v>
       </c>
@@ -8656,7 +8679,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>217</v>
       </c>
@@ -8673,7 +8696,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>218</v>
       </c>
@@ -8690,7 +8713,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>219</v>
       </c>
@@ -8707,7 +8730,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>220</v>
       </c>
@@ -8724,7 +8747,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>221</v>
       </c>
@@ -8741,7 +8764,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>222</v>
       </c>
@@ -8758,7 +8781,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>223</v>
       </c>
@@ -8775,7 +8798,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>224</v>
       </c>
@@ -8792,7 +8815,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>225</v>
       </c>
@@ -8809,7 +8832,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>226</v>
       </c>
@@ -8826,7 +8849,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>227</v>
       </c>
@@ -8843,7 +8866,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>228</v>
       </c>
@@ -8860,7 +8883,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>229</v>
       </c>
@@ -8877,7 +8900,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>230</v>
       </c>
@@ -8894,7 +8917,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>231</v>
       </c>
@@ -8911,7 +8934,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>232</v>
       </c>
@@ -8928,7 +8951,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>233</v>
       </c>
@@ -8945,7 +8968,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>234</v>
       </c>
@@ -8962,7 +8985,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>235</v>
       </c>
@@ -8979,7 +9002,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>236</v>
       </c>
@@ -8996,7 +9019,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>237</v>
       </c>
@@ -9013,7 +9036,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>238</v>
       </c>
@@ -9030,7 +9053,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>239</v>
       </c>
@@ -9047,7 +9070,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>240</v>
       </c>
@@ -9064,7 +9087,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>241</v>
       </c>
@@ -9081,7 +9104,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>242</v>
       </c>
@@ -9098,7 +9121,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>243</v>
       </c>
@@ -9115,7 +9138,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>244</v>
       </c>
@@ -9132,7 +9155,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>245</v>
       </c>
@@ -9149,7 +9172,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>246</v>
       </c>
@@ -9166,7 +9189,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>247</v>
       </c>
@@ -9183,7 +9206,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>248</v>
       </c>
@@ -9200,7 +9223,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>249</v>
       </c>
@@ -9217,7 +9240,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>250</v>
       </c>
@@ -9234,7 +9257,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>251</v>
       </c>
@@ -9251,7 +9274,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>252</v>
       </c>
@@ -9268,7 +9291,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>253</v>
       </c>
@@ -9285,7 +9308,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>254</v>
       </c>
@@ -9302,7 +9325,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>255</v>
       </c>
@@ -9319,7 +9342,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>256</v>
       </c>
@@ -9336,7 +9359,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>257</v>
       </c>
@@ -9353,7 +9376,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>258</v>
       </c>
@@ -9370,7 +9393,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>259</v>
       </c>
@@ -9387,7 +9410,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>260</v>
       </c>
@@ -9404,7 +9427,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>261</v>
       </c>
@@ -9421,7 +9444,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>262</v>
       </c>
@@ -9438,7 +9461,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>263</v>
       </c>
@@ -9455,7 +9478,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>264</v>
       </c>
@@ -9472,7 +9495,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>265</v>
       </c>
@@ -9489,7 +9512,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>266</v>
       </c>
@@ -9506,7 +9529,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>267</v>
       </c>
@@ -9523,7 +9546,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>268</v>
       </c>
@@ -9540,7 +9563,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>269</v>
       </c>
@@ -9557,7 +9580,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>270</v>
       </c>
@@ -9574,7 +9597,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>271</v>
       </c>
@@ -9591,7 +9614,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>272</v>
       </c>
@@ -9608,7 +9631,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>273</v>
       </c>
@@ -9625,7 +9648,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>274</v>
       </c>
@@ -9642,7 +9665,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>275</v>
       </c>
@@ -9659,7 +9682,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>276</v>
       </c>
@@ -9676,7 +9699,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>277</v>
       </c>
@@ -9693,7 +9716,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>278</v>
       </c>
@@ -9710,7 +9733,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>279</v>
       </c>
@@ -9727,7 +9750,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>280</v>
       </c>
@@ -9744,7 +9767,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>281</v>
       </c>
@@ -9761,7 +9784,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>282</v>
       </c>
@@ -9778,7 +9801,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>283</v>
       </c>
@@ -9795,7 +9818,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>284</v>
       </c>
@@ -9812,7 +9835,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>285</v>
       </c>
@@ -9829,7 +9852,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>286</v>
       </c>
@@ -9846,7 +9869,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>287</v>
       </c>
@@ -9863,7 +9886,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>288</v>
       </c>
@@ -9880,7 +9903,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>289</v>
       </c>
@@ -9897,7 +9920,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>290</v>
       </c>
@@ -9914,7 +9937,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>291</v>
       </c>
@@ -9931,7 +9954,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>292</v>
       </c>
@@ -9948,7 +9971,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>293</v>
       </c>
@@ -9965,7 +9988,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>294</v>
       </c>
@@ -9982,7 +10005,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>295</v>
       </c>
@@ -9999,7 +10022,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>296</v>
       </c>
@@ -10016,7 +10039,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>297</v>
       </c>
@@ -10033,7 +10056,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>298</v>
       </c>
@@ -10050,7 +10073,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>299</v>
       </c>
@@ -10067,7 +10090,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>300</v>
       </c>
@@ -10084,7 +10107,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>301</v>
       </c>
@@ -10101,7 +10124,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>302</v>
       </c>
@@ -10118,7 +10141,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>303</v>
       </c>
@@ -10135,7 +10158,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>304</v>
       </c>
@@ -10152,7 +10175,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>305</v>
       </c>
@@ -10169,7 +10192,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>306</v>
       </c>
@@ -10186,7 +10209,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>307</v>
       </c>
@@ -10203,7 +10226,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>308</v>
       </c>
@@ -10220,7 +10243,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>309</v>
       </c>
@@ -10237,7 +10260,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>310</v>
       </c>
@@ -10254,7 +10277,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>311</v>
       </c>
@@ -10271,7 +10294,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>312</v>
       </c>
@@ -10288,7 +10311,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>313</v>
       </c>
@@ -10305,7 +10328,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>314</v>
       </c>
@@ -10322,7 +10345,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>315</v>
       </c>
@@ -10339,7 +10362,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>316</v>
       </c>
@@ -10356,7 +10379,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>317</v>
       </c>
@@ -10373,7 +10396,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>318</v>
       </c>
@@ -10390,7 +10413,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>319</v>
       </c>
@@ -10407,7 +10430,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>320</v>
       </c>
@@ -10424,7 +10447,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>321</v>
       </c>
@@ -10441,7 +10464,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>322</v>
       </c>
@@ -10458,7 +10481,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>323</v>
       </c>
@@ -10475,7 +10498,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>324</v>
       </c>
@@ -10492,7 +10515,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>325</v>
       </c>
@@ -10509,7 +10532,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>326</v>
       </c>
@@ -10526,7 +10549,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>327</v>
       </c>
@@ -10543,7 +10566,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>328</v>
       </c>
@@ -10560,7 +10583,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>329</v>
       </c>
@@ -10577,7 +10600,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>330</v>
       </c>
@@ -10594,7 +10617,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>331</v>
       </c>
@@ -10611,7 +10634,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>332</v>
       </c>
@@ -10628,7 +10651,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>333</v>
       </c>
@@ -10645,7 +10668,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>334</v>
       </c>
@@ -10662,7 +10685,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>335</v>
       </c>
@@ -10679,7 +10702,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>336</v>
       </c>
@@ -10696,7 +10719,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>337</v>
       </c>
@@ -10713,7 +10736,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>338</v>
       </c>
@@ -10730,7 +10753,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>339</v>
       </c>
@@ -10747,7 +10770,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>340</v>
       </c>
@@ -10764,7 +10787,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>341</v>
       </c>
@@ -10781,7 +10804,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>342</v>
       </c>
@@ -10798,7 +10821,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>343</v>
       </c>
@@ -10815,7 +10838,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>344</v>
       </c>
@@ -10832,7 +10855,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>345</v>
       </c>
@@ -10849,7 +10872,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>346</v>
       </c>
@@ -10866,7 +10889,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>347</v>
       </c>
@@ -10883,7 +10906,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>348</v>
       </c>
@@ -10900,7 +10923,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>349</v>
       </c>
@@ -10917,7 +10940,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>350</v>
       </c>
@@ -10934,7 +10957,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>351</v>
       </c>
@@ -10951,7 +10974,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>352</v>
       </c>
@@ -10968,7 +10991,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>353</v>
       </c>
@@ -10985,7 +11008,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>354</v>
       </c>
@@ -11002,7 +11025,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>355</v>
       </c>
@@ -11019,7 +11042,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>356</v>
       </c>
@@ -11036,7 +11059,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>357</v>
       </c>
@@ -11053,7 +11076,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>358</v>
       </c>
@@ -11070,7 +11093,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>359</v>
       </c>
@@ -11087,7 +11110,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>360</v>
       </c>
@@ -11104,7 +11127,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>361</v>
       </c>
@@ -11121,7 +11144,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>362</v>
       </c>
@@ -11138,7 +11161,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>363</v>
       </c>
@@ -11155,7 +11178,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>364</v>
       </c>
@@ -11172,7 +11195,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>365</v>
       </c>
@@ -11189,7 +11212,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>366</v>
       </c>
@@ -11206,7 +11229,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>367</v>
       </c>
@@ -11223,7 +11246,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>368</v>
       </c>
@@ -11240,7 +11263,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>369</v>
       </c>
@@ -11257,7 +11280,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>370</v>
       </c>
@@ -11274,7 +11297,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>371</v>
       </c>
@@ -11291,7 +11314,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>372</v>
       </c>
@@ -11308,7 +11331,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>373</v>
       </c>
@@ -11325,7 +11348,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>374</v>
       </c>
@@ -11342,7 +11365,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>375</v>
       </c>
@@ -11359,7 +11382,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>376</v>
       </c>
@@ -11376,7 +11399,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>377</v>
       </c>
@@ -11393,7 +11416,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>378</v>
       </c>
@@ -11410,7 +11433,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>379</v>
       </c>
@@ -11427,7 +11450,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>380</v>
       </c>
@@ -11444,7 +11467,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>381</v>
       </c>
@@ -11461,7 +11484,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>382</v>
       </c>
@@ -11478,7 +11501,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>383</v>
       </c>
@@ -11495,7 +11518,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>384</v>
       </c>
@@ -11512,7 +11535,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>385</v>
       </c>
@@ -11529,7 +11552,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>386</v>
       </c>
@@ -11546,7 +11569,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>387</v>
       </c>
@@ -11563,7 +11586,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>388</v>
       </c>
@@ -11580,7 +11603,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>389</v>
       </c>
@@ -11597,7 +11620,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>390</v>
       </c>
@@ -11614,7 +11637,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>391</v>
       </c>
@@ -11631,7 +11654,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>392</v>
       </c>
@@ -11648,7 +11671,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>393</v>
       </c>
@@ -11665,7 +11688,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>394</v>
       </c>
@@ -11682,7 +11705,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>395</v>
       </c>
@@ -11699,7 +11722,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>396</v>
       </c>
@@ -11716,7 +11739,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>397</v>
       </c>
@@ -11733,7 +11756,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>398</v>
       </c>
@@ -11750,7 +11773,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>399</v>
       </c>
@@ -11767,7 +11790,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>400</v>
       </c>
@@ -11784,7 +11807,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>401</v>
       </c>
@@ -11801,7 +11824,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>402</v>
       </c>
@@ -11818,7 +11841,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>403</v>
       </c>
@@ -11835,7 +11858,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>404</v>
       </c>
@@ -11852,7 +11875,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>405</v>
       </c>
@@ -11869,7 +11892,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>406</v>
       </c>
@@ -11886,7 +11909,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>407</v>
       </c>
@@ -11903,7 +11926,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>408</v>
       </c>
@@ -11920,7 +11943,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>409</v>
       </c>
@@ -11937,7 +11960,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>410</v>
       </c>
@@ -11954,7 +11977,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>411</v>
       </c>
@@ -11971,7 +11994,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>412</v>
       </c>
@@ -11988,7 +12011,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>413</v>
       </c>
@@ -12005,7 +12028,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>414</v>
       </c>
@@ -12022,7 +12045,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>415</v>
       </c>
@@ -12039,7 +12062,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>416</v>
       </c>
@@ -12056,7 +12079,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>417</v>
       </c>
@@ -12073,7 +12096,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>418</v>
       </c>
@@ -12090,7 +12113,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>419</v>
       </c>
@@ -12107,7 +12130,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>420</v>
       </c>
@@ -12124,7 +12147,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>421</v>
       </c>
@@ -12141,7 +12164,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>422</v>
       </c>
@@ -12158,7 +12181,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>423</v>
       </c>
@@ -12175,7 +12198,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>424</v>
       </c>
@@ -12192,7 +12215,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>425</v>
       </c>
@@ -12209,7 +12232,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>426</v>
       </c>
@@ -12226,7 +12249,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>427</v>
       </c>
@@ -12243,7 +12266,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>428</v>
       </c>
@@ -12260,7 +12283,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>429</v>
       </c>
@@ -12277,7 +12300,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>430</v>
       </c>
@@ -12294,7 +12317,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>431</v>
       </c>
@@ -12311,7 +12334,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>432</v>
       </c>
@@ -12328,7 +12351,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>433</v>
       </c>
@@ -12345,7 +12368,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>434</v>
       </c>
@@ -12362,7 +12385,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>435</v>
       </c>
@@ -12379,7 +12402,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>436</v>
       </c>
@@ -12396,7 +12419,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="428" spans="1:5">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>437</v>
       </c>
@@ -12413,7 +12436,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="429" spans="1:5">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>438</v>
       </c>
@@ -12430,7 +12453,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="430" spans="1:5">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>439</v>
       </c>
@@ -12447,7 +12470,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="431" spans="1:5">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>440</v>
       </c>
@@ -12464,7 +12487,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="432" spans="1:5">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>441</v>
       </c>
@@ -12481,7 +12504,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="433" spans="1:5">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>442</v>
       </c>
@@ -12498,7 +12521,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="434" spans="1:5">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>443</v>
       </c>
@@ -12515,7 +12538,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="435" spans="1:5">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>444</v>
       </c>
@@ -12532,7 +12555,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="436" spans="1:5">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>445</v>
       </c>
@@ -12549,7 +12572,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="437" spans="1:5">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>446</v>
       </c>
@@ -12566,7 +12589,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="438" spans="1:5">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>447</v>
       </c>
@@ -12583,7 +12606,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="439" spans="1:5">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>448</v>
       </c>
@@ -12600,7 +12623,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="440" spans="1:5">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>449</v>
       </c>
@@ -12617,7 +12640,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="441" spans="1:5">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>450</v>
       </c>
@@ -12634,7 +12657,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="442" spans="1:5">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>451</v>
       </c>
@@ -12651,7 +12674,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="443" spans="1:5">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>452</v>
       </c>
@@ -12668,7 +12691,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="444" spans="1:5">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>453</v>
       </c>
@@ -12685,7 +12708,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="445" spans="1:5">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>454</v>
       </c>
@@ -12702,7 +12725,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="446" spans="1:5">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>455</v>
       </c>
@@ -12719,7 +12742,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="447" spans="1:5">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>456</v>
       </c>
@@ -12736,7 +12759,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="448" spans="1:5">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>457</v>
       </c>
@@ -12753,7 +12776,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="449" spans="1:5">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>458</v>
       </c>
@@ -12770,7 +12793,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="450" spans="1:5">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>459</v>
       </c>
@@ -12787,7 +12810,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="451" spans="1:5">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>460</v>
       </c>
@@ -12804,7 +12827,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="452" spans="1:5">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>461</v>
       </c>
@@ -12821,7 +12844,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="453" spans="1:5">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>462</v>
       </c>
@@ -12838,7 +12861,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="454" spans="1:5">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>463</v>
       </c>
@@ -12855,7 +12878,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="455" spans="1:5">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>464</v>
       </c>
@@ -12872,7 +12895,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="456" spans="1:5">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>465</v>
       </c>
@@ -12889,7 +12912,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="457" spans="1:5">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>466</v>
       </c>
@@ -12906,7 +12929,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="458" spans="1:5">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>467</v>
       </c>
@@ -12923,7 +12946,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="459" spans="1:5">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>468</v>
       </c>
@@ -12940,7 +12963,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="460" spans="1:5">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>469</v>
       </c>
@@ -12957,7 +12980,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="461" spans="1:5">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>470</v>
       </c>
@@ -12974,7 +12997,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="462" spans="1:5">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>471</v>
       </c>
@@ -12991,7 +13014,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="463" spans="1:5">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>472</v>
       </c>
@@ -13008,7 +13031,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="464" spans="1:5">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>473</v>
       </c>
@@ -13025,7 +13048,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="465" spans="1:5">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>474</v>
       </c>
@@ -13042,7 +13065,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="466" spans="1:5">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>475</v>
       </c>
@@ -13059,7 +13082,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="467" spans="1:5">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>476</v>
       </c>
@@ -13076,7 +13099,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="468" spans="1:5">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>477</v>
       </c>
@@ -13093,7 +13116,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="469" spans="1:5">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>478</v>
       </c>
@@ -13110,7 +13133,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="470" spans="1:5">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>479</v>
       </c>
@@ -13127,7 +13150,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="471" spans="1:5">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>480</v>
       </c>
@@ -13144,7 +13167,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="472" spans="1:5">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>481</v>
       </c>
@@ -13161,7 +13184,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="473" spans="1:5">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>482</v>
       </c>
@@ -13178,7 +13201,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="474" spans="1:5">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>483</v>
       </c>
@@ -13195,7 +13218,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="475" spans="1:5">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>484</v>
       </c>
@@ -13212,7 +13235,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="476" spans="1:5">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>485</v>
       </c>
@@ -13229,7 +13252,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="477" spans="1:5">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>486</v>
       </c>
@@ -13246,7 +13269,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="478" spans="1:5">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>487</v>
       </c>
@@ -13263,7 +13286,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="479" spans="1:5">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>488</v>
       </c>
@@ -13280,7 +13303,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="480" spans="1:5">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>489</v>
       </c>
@@ -13297,7 +13320,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="481" spans="1:5">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>490</v>
       </c>
@@ -13314,7 +13337,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="482" spans="1:5">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>491</v>
       </c>
@@ -13331,7 +13354,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="483" spans="1:5">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>492</v>
       </c>
@@ -13348,7 +13371,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="484" spans="1:5">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>493</v>
       </c>
@@ -13365,7 +13388,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="485" spans="1:5">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>494</v>
       </c>
@@ -13382,7 +13405,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="486" spans="1:5">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>495</v>
       </c>
@@ -13399,7 +13422,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="487" spans="1:5">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>496</v>
       </c>
@@ -13416,7 +13439,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="488" spans="1:5">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>497</v>
       </c>
@@ -13433,7 +13456,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="489" spans="1:5">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>498</v>
       </c>
@@ -13450,7 +13473,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="490" spans="1:5">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>499</v>
       </c>
@@ -13467,7 +13490,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="491" spans="1:5">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>500</v>
       </c>
@@ -13484,7 +13507,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="492" spans="1:5">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>501</v>
       </c>
@@ -13501,7 +13524,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="493" spans="1:5">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>502</v>
       </c>
@@ -13518,7 +13541,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="494" spans="1:5">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>503</v>
       </c>
@@ -13535,7 +13558,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="495" spans="1:5">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>504</v>
       </c>
@@ -13552,7 +13575,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="496" spans="1:5">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>505</v>
       </c>
@@ -13569,7 +13592,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="497" spans="1:5">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>506</v>
       </c>
@@ -13586,7 +13609,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="498" spans="1:5">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>507</v>
       </c>
@@ -13603,7 +13626,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="499" spans="1:5">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>508</v>
       </c>
@@ -13620,7 +13643,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="500" spans="1:5">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>509</v>
       </c>
@@ -13637,7 +13660,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="501" spans="1:5">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>510</v>
       </c>
@@ -13654,7 +13677,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="502" spans="1:5">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>511</v>
       </c>
@@ -13671,7 +13694,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="503" spans="1:5">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>512</v>
       </c>
@@ -13688,7 +13711,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="504" spans="1:5">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>513</v>
       </c>
@@ -13705,7 +13728,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="505" spans="1:5">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>514</v>
       </c>
@@ -13722,7 +13745,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="506" spans="1:5">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>515</v>
       </c>
@@ -13739,7 +13762,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="507" spans="1:5">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
         <v>516</v>
       </c>
@@ -13756,7 +13779,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="508" spans="1:5">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>517</v>
       </c>
@@ -13773,7 +13796,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="509" spans="1:5">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>518</v>
       </c>
@@ -13790,7 +13813,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="510" spans="1:5">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
         <v>519</v>
       </c>
@@ -13807,7 +13830,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="511" spans="1:5">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
         <v>520</v>
       </c>
@@ -13824,7 +13847,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="512" spans="1:5">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
         <v>521</v>
       </c>
@@ -13841,7 +13864,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="513" spans="1:5">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
         <v>522</v>
       </c>
@@ -13858,7 +13881,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="514" spans="1:5">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>523</v>
       </c>
@@ -13875,7 +13898,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="515" spans="1:5">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>524</v>
       </c>
@@ -13892,7 +13915,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="516" spans="1:5">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>525</v>
       </c>
@@ -13909,7 +13932,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="517" spans="1:5">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>526</v>
       </c>
@@ -13926,7 +13949,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="518" spans="1:5">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>527</v>
       </c>
@@ -13943,7 +13966,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="519" spans="1:5">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>528</v>
       </c>
@@ -13960,7 +13983,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="520" spans="1:5">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
         <v>529</v>
       </c>
@@ -13977,7 +14000,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="521" spans="1:5">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
         <v>530</v>
       </c>
@@ -13994,7 +14017,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="522" spans="1:5">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
         <v>531</v>
       </c>
@@ -14011,7 +14034,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="523" spans="1:5">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
         <v>532</v>
       </c>
@@ -14028,7 +14051,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="524" spans="1:5">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
         <v>533</v>
       </c>
@@ -14045,7 +14068,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="525" spans="1:5">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
         <v>534</v>
       </c>
@@ -14062,7 +14085,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="526" spans="1:5">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
         <v>535</v>
       </c>
@@ -14079,7 +14102,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="527" spans="1:5">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
         <v>536</v>
       </c>
@@ -14096,7 +14119,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="528" spans="1:5">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
         <v>537</v>
       </c>
@@ -14113,7 +14136,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="529" spans="1:5">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
         <v>538</v>
       </c>
@@ -14130,7 +14153,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="530" spans="1:5">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
         <v>539</v>
       </c>
@@ -14147,7 +14170,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="531" spans="1:5">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
         <v>540</v>
       </c>
@@ -14164,7 +14187,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="532" spans="1:5">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
         <v>541</v>
       </c>
@@ -14181,7 +14204,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="533" spans="1:5">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
         <v>542</v>
       </c>
@@ -14198,7 +14221,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="534" spans="1:5">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
         <v>543</v>
       </c>
@@ -14215,7 +14238,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="535" spans="1:5">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
         <v>544</v>
       </c>
@@ -14232,7 +14255,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="536" spans="1:5">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
         <v>545</v>
       </c>
@@ -14249,7 +14272,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="537" spans="1:5">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
         <v>546</v>
       </c>
@@ -14266,7 +14289,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="538" spans="1:5">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
         <v>547</v>
       </c>
@@ -14283,7 +14306,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="539" spans="1:5">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
         <v>548</v>
       </c>
@@ -14300,7 +14323,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="540" spans="1:5">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
         <v>549</v>
       </c>
@@ -14317,7 +14340,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="541" spans="1:5">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
         <v>550</v>
       </c>
@@ -14334,7 +14357,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="542" spans="1:5">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
         <v>551</v>
       </c>
@@ -14351,7 +14374,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="543" spans="1:5">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
         <v>552</v>
       </c>
@@ -14368,7 +14391,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="544" spans="1:5">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
         <v>553</v>
       </c>
@@ -14385,7 +14408,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="545" spans="1:5">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
         <v>554</v>
       </c>
@@ -14402,7 +14425,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="546" spans="1:5">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
         <v>555</v>
       </c>
@@ -14419,7 +14442,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="547" spans="1:5">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
         <v>556</v>
       </c>
@@ -14436,7 +14459,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="548" spans="1:5">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
         <v>557</v>
       </c>
@@ -14453,7 +14476,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="549" spans="1:5">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
         <v>558</v>
       </c>
@@ -14470,7 +14493,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="550" spans="1:5">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
         <v>559</v>
       </c>
@@ -14487,7 +14510,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="551" spans="1:5">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
         <v>560</v>
       </c>
@@ -14504,7 +14527,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="552" spans="1:5">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
         <v>561</v>
       </c>
@@ -14521,7 +14544,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="553" spans="1:5">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
         <v>562</v>
       </c>
@@ -14538,7 +14561,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="554" spans="1:5">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
         <v>563</v>
       </c>
@@ -14555,7 +14578,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="555" spans="1:5">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
         <v>564</v>
       </c>
@@ -14572,7 +14595,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="556" spans="1:5">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
         <v>565</v>
       </c>
@@ -14589,7 +14612,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="557" spans="1:5">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
         <v>566</v>
       </c>
@@ -14606,7 +14629,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="558" spans="1:5">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
         <v>567</v>
       </c>
@@ -14623,7 +14646,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="559" spans="1:5">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
         <v>568</v>
       </c>
@@ -14640,7 +14663,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="560" spans="1:5">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
         <v>569</v>
       </c>
@@ -14657,7 +14680,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="561" spans="1:5">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
         <v>570</v>
       </c>
@@ -14674,7 +14697,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="562" spans="1:5">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
         <v>571</v>
       </c>
@@ -14691,7 +14714,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="563" spans="1:5">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
         <v>572</v>
       </c>
@@ -14708,7 +14731,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="564" spans="1:5">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
         <v>573</v>
       </c>
@@ -14725,7 +14748,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="565" spans="1:5">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
         <v>574</v>
       </c>
@@ -14742,7 +14765,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="566" spans="1:5">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
         <v>575</v>
       </c>
@@ -14759,7 +14782,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="567" spans="1:5">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
         <v>576</v>
       </c>
@@ -14776,7 +14799,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="568" spans="1:5">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
         <v>577</v>
       </c>
@@ -14793,7 +14816,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="569" spans="1:5">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
         <v>578</v>
       </c>
@@ -14810,7 +14833,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="570" spans="1:5">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A570" t="s">
         <v>579</v>
       </c>
@@ -14827,7 +14850,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="571" spans="1:5">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A571" t="s">
         <v>580</v>
       </c>
@@ -14844,7 +14867,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="572" spans="1:5">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A572" t="s">
         <v>581</v>
       </c>
@@ -14861,7 +14884,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="573" spans="1:5">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A573" t="s">
         <v>582</v>
       </c>
@@ -14878,7 +14901,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="574" spans="1:5">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
         <v>583</v>
       </c>
@@ -14895,7 +14918,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="575" spans="1:5">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
         <v>584</v>
       </c>
@@ -14912,7 +14935,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="576" spans="1:5">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
         <v>585</v>
       </c>
@@ -14929,7 +14952,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="577" spans="1:5">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
         <v>586</v>
       </c>
@@ -14946,7 +14969,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="578" spans="1:5">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A578" t="s">
         <v>587</v>
       </c>
@@ -14963,7 +14986,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="579" spans="1:5">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
         <v>588</v>
       </c>
@@ -14980,7 +15003,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="580" spans="1:5">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A580" t="s">
         <v>589</v>
       </c>
@@ -14997,7 +15020,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="581" spans="1:5">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A581" t="s">
         <v>590</v>
       </c>
@@ -15014,7 +15037,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="582" spans="1:5">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A582" t="s">
         <v>591</v>
       </c>
@@ -15031,7 +15054,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="583" spans="1:5">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A583" t="s">
         <v>592</v>
       </c>
@@ -15048,7 +15071,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="584" spans="1:5">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A584" t="s">
         <v>593</v>
       </c>
@@ -15065,7 +15088,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="585" spans="1:5">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A585" t="s">
         <v>594</v>
       </c>
@@ -15082,7 +15105,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="586" spans="1:5">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
         <v>595</v>
       </c>
@@ -15099,7 +15122,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="587" spans="1:5">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
         <v>596</v>
       </c>
@@ -15116,7 +15139,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="588" spans="1:5">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
         <v>597</v>
       </c>
@@ -15133,7 +15156,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="589" spans="1:5">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
         <v>598</v>
       </c>
@@ -15150,7 +15173,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="590" spans="1:5">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
         <v>599</v>
       </c>
@@ -15167,7 +15190,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="591" spans="1:5">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A591" t="s">
         <v>600</v>
       </c>
@@ -15184,7 +15207,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="592" spans="1:5">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A592" t="s">
         <v>601</v>
       </c>
@@ -15201,7 +15224,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="593" spans="1:5">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A593" t="s">
         <v>602</v>
       </c>
@@ -15218,7 +15241,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="594" spans="1:5">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A594" t="s">
         <v>603</v>
       </c>
@@ -15235,7 +15258,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="595" spans="1:5">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
         <v>604</v>
       </c>
@@ -15252,7 +15275,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="596" spans="1:5">
+    <row r="596" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A596" t="s">
         <v>605</v>
       </c>
@@ -15269,7 +15292,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="597" spans="1:5">
+    <row r="597" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A597" t="s">
         <v>606</v>
       </c>
@@ -15286,7 +15309,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="598" spans="1:5">
+    <row r="598" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A598" t="s">
         <v>607</v>
       </c>
@@ -15303,7 +15326,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="599" spans="1:5">
+    <row r="599" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A599" t="s">
         <v>608</v>
       </c>
@@ -15320,7 +15343,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="600" spans="1:5">
+    <row r="600" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A600" t="s">
         <v>609</v>
       </c>
@@ -15337,7 +15360,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="601" spans="1:5">
+    <row r="601" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A601" t="s">
         <v>610</v>
       </c>
@@ -15354,7 +15377,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="602" spans="1:5">
+    <row r="602" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A602" t="s">
         <v>611</v>
       </c>
@@ -15371,7 +15394,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="603" spans="1:5">
+    <row r="603" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A603" t="s">
         <v>612</v>
       </c>
@@ -15388,7 +15411,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="604" spans="1:5">
+    <row r="604" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
         <v>613</v>
       </c>
@@ -15405,7 +15428,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="605" spans="1:5">
+    <row r="605" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A605" t="s">
         <v>614</v>
       </c>
@@ -15422,7 +15445,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="606" spans="1:5">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A606" t="s">
         <v>615</v>
       </c>
@@ -15439,7 +15462,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="607" spans="1:5">
+    <row r="607" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A607" t="s">
         <v>616</v>
       </c>
@@ -15456,7 +15479,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="608" spans="1:5">
+    <row r="608" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A608" t="s">
         <v>617</v>
       </c>
@@ -15473,7 +15496,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="609" spans="1:5">
+    <row r="609" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A609" t="s">
         <v>618</v>
       </c>
@@ -15490,7 +15513,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="610" spans="1:5">
+    <row r="610" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A610" t="s">
         <v>619</v>
       </c>
@@ -15507,7 +15530,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="611" spans="1:5">
+    <row r="611" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A611" t="s">
         <v>620</v>
       </c>
@@ -15524,7 +15547,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="612" spans="1:5">
+    <row r="612" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A612" t="s">
         <v>621</v>
       </c>
@@ -15541,7 +15564,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="613" spans="1:5">
+    <row r="613" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
         <v>622</v>
       </c>
@@ -15558,7 +15581,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="614" spans="1:5">
+    <row r="614" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A614" t="s">
         <v>623</v>
       </c>
@@ -15575,7 +15598,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="615" spans="1:5">
+    <row r="615" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A615" t="s">
         <v>624</v>
       </c>
@@ -15592,7 +15615,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="616" spans="1:5">
+    <row r="616" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A616" t="s">
         <v>625</v>
       </c>
@@ -15609,7 +15632,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="617" spans="1:5">
+    <row r="617" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A617" t="s">
         <v>626</v>
       </c>
@@ -15626,7 +15649,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="618" spans="1:5">
+    <row r="618" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A618" t="s">
         <v>627</v>
       </c>
@@ -15643,7 +15666,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="619" spans="1:5">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A619" t="s">
         <v>628</v>
       </c>
@@ -15660,7 +15683,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="620" spans="1:5">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
         <v>629</v>
       </c>
@@ -15677,7 +15700,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="621" spans="1:5">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A621" t="s">
         <v>630</v>
       </c>
@@ -15694,7 +15717,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="622" spans="1:5">
+    <row r="622" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
         <v>631</v>
       </c>
@@ -15711,7 +15734,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="623" spans="1:5">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A623" t="s">
         <v>632</v>
       </c>
@@ -15728,7 +15751,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="624" spans="1:5">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A624" t="s">
         <v>633</v>
       </c>
@@ -15745,7 +15768,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="625" spans="1:5">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A625" t="s">
         <v>634</v>
       </c>
@@ -15762,7 +15785,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="626" spans="1:5">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A626" t="s">
         <v>635</v>
       </c>
@@ -15779,7 +15802,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="627" spans="1:5">
+    <row r="627" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A627" t="s">
         <v>636</v>
       </c>
@@ -15796,7 +15819,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="628" spans="1:5">
+    <row r="628" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A628" t="s">
         <v>637</v>
       </c>
@@ -15813,7 +15836,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="629" spans="1:5">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A629" t="s">
         <v>638</v>
       </c>
@@ -15830,7 +15853,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="630" spans="1:5">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A630" t="s">
         <v>639</v>
       </c>
@@ -15847,7 +15870,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="631" spans="1:5">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
         <v>640</v>
       </c>
@@ -15864,7 +15887,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="632" spans="1:5">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A632" t="s">
         <v>641</v>
       </c>
@@ -15881,7 +15904,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="633" spans="1:5">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A633" t="s">
         <v>642</v>
       </c>
@@ -15898,7 +15921,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="634" spans="1:5">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A634" t="s">
         <v>643</v>
       </c>
@@ -15915,7 +15938,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="635" spans="1:5">
+    <row r="635" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A635" t="s">
         <v>644</v>
       </c>
@@ -15932,7 +15955,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="636" spans="1:5">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A636" t="s">
         <v>645</v>
       </c>
@@ -15949,7 +15972,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="637" spans="1:5">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A637" t="s">
         <v>646</v>
       </c>
@@ -15966,7 +15989,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="638" spans="1:5">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A638" t="s">
         <v>647</v>
       </c>
@@ -15983,7 +16006,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="639" spans="1:5">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A639" t="s">
         <v>648</v>
       </c>
@@ -16000,7 +16023,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="640" spans="1:5">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
         <v>649</v>
       </c>
@@ -16017,7 +16040,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="641" spans="1:5">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A641" t="s">
         <v>650</v>
       </c>
@@ -16034,7 +16057,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="642" spans="1:5">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A642" t="s">
         <v>651</v>
       </c>
@@ -16051,7 +16074,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="643" spans="1:5">
+    <row r="643" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A643" t="s">
         <v>652</v>
       </c>
@@ -16068,7 +16091,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="644" spans="1:5">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A644" t="s">
         <v>653</v>
       </c>
@@ -16085,7 +16108,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="645" spans="1:5">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A645" t="s">
         <v>654</v>
       </c>
@@ -16102,7 +16125,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="646" spans="1:5">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A646" t="s">
         <v>655</v>
       </c>
@@ -16119,7 +16142,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="647" spans="1:5">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A647" t="s">
         <v>656</v>
       </c>
@@ -16136,7 +16159,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="648" spans="1:5">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A648" t="s">
         <v>657</v>
       </c>
@@ -16153,7 +16176,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="649" spans="1:5">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
         <v>658</v>
       </c>
@@ -16170,7 +16193,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="650" spans="1:5">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A650" t="s">
         <v>659</v>
       </c>
@@ -16187,7 +16210,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="651" spans="1:5">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
         <v>660</v>
       </c>
@@ -16204,7 +16227,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="652" spans="1:5">
+    <row r="652" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A652" t="s">
         <v>661</v>
       </c>
@@ -16221,7 +16244,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="653" spans="1:5">
+    <row r="653" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A653" t="s">
         <v>662</v>
       </c>
@@ -16238,7 +16261,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="654" spans="1:5">
+    <row r="654" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A654" t="s">
         <v>663</v>
       </c>
@@ -16255,7 +16278,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="655" spans="1:5">
+    <row r="655" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A655" t="s">
         <v>664</v>
       </c>
@@ -16272,7 +16295,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="656" spans="1:5">
+    <row r="656" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A656" t="s">
         <v>665</v>
       </c>
@@ -16289,7 +16312,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="657" spans="1:5">
+    <row r="657" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A657" t="s">
         <v>666</v>
       </c>
@@ -16306,7 +16329,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="658" spans="1:5">
+    <row r="658" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A658" t="s">
         <v>667</v>
       </c>
@@ -16323,7 +16346,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="659" spans="1:5">
+    <row r="659" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A659" t="s">
         <v>668</v>
       </c>
@@ -16340,7 +16363,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="660" spans="1:5">
+    <row r="660" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A660" t="s">
         <v>669</v>
       </c>
@@ -16358,6 +16381,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K660" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>